--- a/resumo_multas.xlsx
+++ b/resumo_multas.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -47,8 +50,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,1181 +469,2249 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>data_infracao</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>hora_infracao</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>dias_para_vencimento</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>valor_num</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>codigo_infracao</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>descricao_infracao</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>local_infracao</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>uf</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>codigo_municipio</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>codigo_orgao</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>orgao_autuador</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>proprietario</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>marca_modelo</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>arquivo</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>caminho</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>valor_num</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>a_vencer</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>A_Vencer</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Autuacao</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>J010624082</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>000100J0106240827455</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>R$ 130,16</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>130.16</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>7455</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>TRANSITAR EM VELOCIDADE SUPERIOR A MAXIMA PERMITIDA EM ATE</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>SP - BR 381 - KM 70.20 - DECRESCENTE</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>MAIRIPORA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>26/10/2026</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>TRANSITAR EM VELOCIDADE SUPERIOR A MAXIMA PERMITIDA EM ATE DATA LIMITE PARA IDENTIFICAÇÃO DO CONDUTOR INFRATOR 20% 26/10/2026</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (Número do AIT) MAIRIPORA SP J010624082 IDENTIFICAÇÃO DA INFRAÇÃO DATA DA NOTIFICAÇÃO DA AUTUAÇÃO 06/09/2026</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>REGISTRO FOTOGRÁFICO JOANOPOLIS AGROPECUARIA LTDA EPP</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO R07334 IDENTIFICAÇÃO DO CONDUTOR</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>6671</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>000100</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>POLICIA RODOVIARIA FEDERAL</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>notificacaoAutuacao_BSC4C89_000100J0106240827455.pdf</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\a_vencer\notificacaoAutuacao_BSC4C89_000100J0106240827455.pdf</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>a_vencer</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>26/08/2026</t>
-        </is>
+          <t>A_Vencer</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Autuacao</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1AA9702755</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1262001AA97027555002</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>46260</v>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>02/10/2026</t>
-        </is>
+      <c r="H3" s="1" t="n">
+        <v>46297</v>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>MULTA, POR NAO IDENTIFICACAO DO CONDUTOR INFRATOR, IMPOSTA DATA LIMITE PARA IDENTIFICAÇÃO DO CONDUTOR INFRATOR A PESSOA JURIDICA Não se aplica</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (Número do AIT) BRAGANCA PAULISTA SP 1AA9702755 IDENTIFICAÇÃO DA INFRAÇÃO DATA DA NOTIFICAÇÃO DA AUTUAÇÃO 26/08/2026</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 260,32</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>260.32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>REGISTRO FOTOGRÁFICO JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>MULTA, POR NAO IMPOSTA</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>SP 008 KM 096 METROS 860</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>BRAGANCA PAULISTA</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6251</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>126200</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>DER - SP</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>notificacaoAutuacao_BSC4C89_1262001AA97027555002.pdf</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\a_vencer\notificacaoAutuacao_BSC4C89_1262001AA97027555002.pdf</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a_vencer</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>A_Vencer</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Autuacao</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>R480598546</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>266710R4805985465746</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>R$ 130,16</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>130.16</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5746</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>TRANSITAR EM LOCAL/HORARIO NAO PERMITIDO PELA</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>AV. LEONOR DE OLIVEIRA, 251</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>MAIRIPORA</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>15/09/2026</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>29/10/2026</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>TRANSITAR EM LOCAL/HORARIO NAO PERMITIDO PELA DATA LIMITE PARA IDENTIFICAÇÃO DO CONDUTOR INFRATOR REGULAMENTACAO - RODIZIO 29/10/2026</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (Número do AIT) MAIRIPORA SP R480598546 IDENTIFICAÇÃO DA INFRAÇÃO DATA DA NOTIFICAÇÃO DA AUTUAÇÃO 15/09/2026</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>REGISTRO FOTOGRÁFICO JOANOPOLIS AGROPECUARIA LTDA EPP</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>6671</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>266710</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>PREF. DE SP MAIRIPORA</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>notificacaoAutuacao_BSC4C89_266710R4805985465746.pdf</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\a_vencer\notificacaoAutuacao_BSC4C89_266710R4805985465746.pdf</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>a_vencer</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>A_Vencer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>J007389472</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>000100J0073894727455</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>46365</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" s="1" t="n">
+        <v>46365</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>63</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>R$ 130,16</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>130.16</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>7455</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>TRANSITAR EM VELOCIDADE SUPERIOR A MAXIMA PERMITIDA EM ATE</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>SP - BR 381 - KM 70.20 - D</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>MAIRIPORA</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>09/12/2026</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM TRANSITAR EM VELOCIDADE SUPERIOR A MAXIMA PERMITIDA EM ATE DESCONTO) 20% 09/12/2026</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) MAIRIPORA SP J007389472 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 11/08/2026</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>REGISTRO FOTOGRÁFICO JOANOPOLIS AGROPECUARIA LTDA EPP</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO R07334 IDENTIFICAÇÃO DO CONDUTOR</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>6671</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>000100</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>POLICIA RODOVIARIA FEDERAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>notificacaoPenalidade_BSC4C89_000100J0073894727455.pdf</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\a_vencer\notificacaoPenalidade_BSC4C89_000100J0073894727455.pdf</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>a_vencer</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
+          <t>A_Vencer</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1AA6014095</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1262001AA60140955002</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>46308</v>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" s="1" t="n">
+        <v>46308</v>
+      </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM MULTA, POR NAO IDENTIFICACAO DO CONDUTOR INFRATOR, IMPOSTA DESCONTO) A PESSOA JURIDICA 13/10/2026</t>
-        </is>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) PIRACAIA SP 1AA6014095 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 31/08/2026</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 260,32</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>260.32</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>REGISTRO FOTOGRÁFICO JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>MULTA, POR NAO IMPOSTA</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>SP 036 KM 080 METROS 929</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>PIRACAIA</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>6873</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>126200</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>DER - SP</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_1262001AA60140955002.pdf</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\a_vencer\notificacaoPenalidade_BSC4C89_1262001AA60140955002.pdf</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>a_vencer</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>23/10/2026</t>
-        </is>
+          <t>A_Vencer</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Z147044804</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>262910Z1470448045002</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>46318</v>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" s="1" t="n">
+        <v>46318</v>
+      </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM MULTA, POR NAO IDENTIFICACAO DO CONDUTOR INFRATOR, IMPOSTA DESCONTO) A PESSOA JURIDICA 23/10/2026</t>
-        </is>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>16</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) CAMPINAS SP Z147044804 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 17/09/2026</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 586,94</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>586.9400000000001</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>REGISTRO FOTOGRÁFICO JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>MULTA, POR NAO IMPOSTA</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>RUA ANTONIO MANUEL, 50 - VILA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>CAMPINAS</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>6291</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>262910</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>PREF. DE SP CAMPINAS</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_262910Z1470448045002.pdf</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\a_vencer\notificacaoPenalidade_BSC4C89_262910Z1470448045002.pdf</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>a_vencer</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>A_Vencer</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>R480588746</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>266710R4805887465746</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>46329</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" s="1" t="n">
+        <v>46329</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>27</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>R$ 130,16</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>130.16</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5746</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>TRANSITAR EM LOCAL/HORARIO NAO PERMITIDO PELA</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>AV. LEONOR DE OLIVEIRA, 251</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>MAIRIPORA</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>03/11/2026</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM TRANSITAR EM LOCAL/HORARIO NAO PERMITIDO PELA DESCONTO) REGULAMENTACAO - RODIZIO 03/11/2026</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) MAIRIPORA SP R480588746 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 16/09/2026</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>REGISTRO FOTOGRÁFICO JOANOPOLIS AGROPECUARIA LTDA EPP</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>6671</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>266710</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>PREF. DE SP MAIRIPORA</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>notificacaoPenalidade_BSC4C89_266710R4805887465746.pdf</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\a_vencer\notificacaoPenalidade_BSC4C89_266710R4805887465746.pdf</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pagas</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Pagas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
+          <t>N490064686</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>264270N4900646865002</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>46199</v>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
+      <c r="I9" s="1" t="n">
+        <v>46199</v>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM MULTA, POR NAO IDENTIFICACAO DO CONDUTOR INFRATOR, IMPOSTA DESCONTO) A PESSOA JURIDICA 26/06/2026</t>
-        </is>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>-103</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) FRANCISCO MORATO SP N490064686 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 12/05/2026</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 586,94</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>586.9400000000001</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>JOANOPOLIS AGROPECUARIA LTDA EPP REGISTRO FOTOGRÁFICO</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>MULTA, POR NAO IMPOSTA</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>AV PAULO BROSSARD 1011</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>FRANCISCO MORATO</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>6427</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>264270</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>PREF. DE SP FRANCISCO</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_264270N4900646865002.pdf</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\pagas\notificacaoPenalidade_BSC4C89_264270N4900646865002.pdf</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>vencidas</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>23/02/2026</t>
-        </is>
+          <t>Vencidas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1AA0994533</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1262001AA09945335002</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>46076</v>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" s="1" t="n">
+        <v>46076</v>
+      </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM MULTA, POR NAO IDENTIFICACAO DO CONDUTOR INFRATOR, IMPOSTA DESCONTO) A PESSOA JURIDICA 23/02/2026</t>
-        </is>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>-226</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) LOUVEIRA SP 1AA0994533 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 12/01/2026</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 390,46</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>390.46</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>REGISTRO FOTOGRÁFICO JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>MULTA, POR NAO IMPOSTA</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>SP 063 KM 000 METROS 020</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LOUVEIRA</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>6647</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>126200</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>DER - SP</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_1262001AA09945335002.pdf</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\vencidas\notificacaoPenalidade_BSC4C89_1262001AA09945335002.pdf</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>vencidas</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>12/01/2026</t>
-        </is>
+          <t>Vencidas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1DJ1739941</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1262001DJ17399415185</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>46034</v>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" s="1" t="n">
+        <v>46034</v>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM DEIXAR O PASSAGEIRO DE USAR O CINTO SEGURANCA DESCONTO) 12/01/2026</t>
-        </is>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>-268</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) LOUVEIRA SP 1DJ1739941 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 01/12/2025</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 195,23</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>195.23</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>JOANOPOLIS AGROPECUARIA LTDA EPP REGISTRO FOTOGRÁFICO</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>DEIXAR O PASSAGEIRO DE USAR O CINTO SEGURANCA</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>SP 063 KM 000 METROS 020</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>LOUVEIRA</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>6647</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>126200</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>DER - SP</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_1262001DJ17399415185.pdf</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\vencidas\notificacaoPenalidade_BSC4C89_1262001DJ17399415185.pdf</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>vencidas</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
-        </is>
+          <t>Vencidas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1DJ2887241</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1262001DJ28872415185</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>46014</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>46055</v>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" s="1" t="n">
+        <v>46055</v>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM DEIXAR O CONDUTOR DE USAR O CINTO SEGURANCA DESCONTO) 02/02/2026</t>
-        </is>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>-247</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) ATIBAIA SP 1DJ2887241 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 23/12/2025</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 195,23</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>195.23</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>JOANOPOLIS AGROPECUARIA LTDA EPP REGISTRO FOTOGRÁFICO</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>DEIXAR O USAR O CINTO SEGURANCA</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>SPD 068/065 KM 000 METROS 500</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>ATIBAIA</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>6181</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>126200</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>DER - SP</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_1262001DJ28872415185.pdf</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\vencidas\notificacaoPenalidade_BSC4C89_1262001DJ28872415185.pdf</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>vencidas</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
+          <t>Vencidas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1DK3774611</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1262001DK37746115185</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>46174</v>
       </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" s="1" t="n">
+        <v>46174</v>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM DEIXAR O CONDUTOR DE USAR O CINTO SEGURANCA DESCONTO) 01/06/2026</t>
-        </is>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>-128</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) CAMPINAS SP 1DK3774611 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 22/04/2026</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 195,23</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>195.23</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>JOANOPOLIS AGROPECUARIA LTDA EPP REGISTRO FOTOGRÁFICO</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>DEIXAR O USAR O CINTO SEGURANCA</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>SP 340 KM 117 METROS 900</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>CAMPINAS</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>6291</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>126200</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>DER - SP</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_1262001DK37746115185.pdf</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\vencidas\notificacaoPenalidade_BSC4C89_1262001DK37746115185.pdf</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>vencidas</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>29/12/2025</t>
-        </is>
+          <t>Vencidas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1VA0048671</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1262001VA00486717455</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>46020</v>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" s="1" t="n">
+        <v>46020</v>
+      </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM TRANSITAR EM VELOCIDADE SUPERIOR A MAXIMA PERMITIDA EM ATE DESCONTO) 20% 29/12/2025</t>
-        </is>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>-282</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) CAMPO LIMPO PAULISTA SP 1VA0048671 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 17/11/2025</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 130,16</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>130.16</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>REGISTRO FOTOGRÁFICO JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>TRANSITAR EM VELOCIDADE SUPERIOR A MAXIMA PERMITIDA EM ATE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
+          <t>SP 354 KM 058 METROS 072</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>CAMPO LIMPO PAULISTA</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>6293</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>126200</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>DER - SP</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_1262001VA00486717455.pdf</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\vencidas\notificacaoPenalidade_BSC4C89_1262001VA00486717455.pdf</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>vencidas</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>17/08/2026</t>
-        </is>
+          <t>Vencidas</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1VA3059620</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1262001VA30596207455</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>46251</v>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" s="1" t="n">
+        <v>46251</v>
+      </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM TRANSITAR EM VELOCIDADE SUPERIOR A MAXIMA PERMITIDA EM ATE DESCONTO) 20% 17/08/2026</t>
-        </is>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>-51</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) PIRACAIA SP 1VA3059620 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 08/07/2026</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 130,16</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>130.16</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>REGISTRO FOTOGRÁFICO JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>TRANSITAR EM VELOCIDADE SUPERIOR A MAXIMA PERMITIDA EM ATE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
+          <t>SP 036 KM 080 METROS 929</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>PIRACAIA</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>6873</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>126200</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>DER - SP</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_1262001VA30596207455.pdf</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\vencidas\notificacaoPenalidade_BSC4C89_1262001VA30596207455.pdf</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>vencidas</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
+          <t>Vencidas</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1VA3860791</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1262001VA38607917455</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>46300</v>
       </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" s="1" t="n">
+        <v>46300</v>
+      </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM TRANSITAR EM VELOCIDADE SUPERIOR A MAXIMA PERMITIDA EM ATE DESCONTO) 20% 05/10/2026</t>
-        </is>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>-2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) BRAGANCA PAULISTA SP 1VA3860791 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 25/08/2026</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 130,16</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>130.16</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>REGISTRO FOTOGRÁFICO JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>TRANSITAR EM VELOCIDADE SUPERIOR A MAXIMA PERMITIDA EM ATE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>SP 008 KM 096 METROS 860</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>BRAGANCA PAULISTA</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>6251</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>126200</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>DER - SP</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_1262001VA38607917455.pdf</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\vencidas\notificacaoPenalidade_BSC4C89_1262001VA38607917455.pdf</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>vencidas</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
+          <t>Vencidas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A075926715</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>262910A0759267155185</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>46128</v>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" s="1" t="n">
+        <v>46128</v>
+      </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM DEIXAR O CONDUTOR DE USAR O CINTO SEGURANCA DESCONTO) 16/04/2026</t>
-        </is>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>-174</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) CAMPINAS SP A075926715 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 11/03/2026</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 195,23</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>195.23</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>JOANOPOLIS AGROPECUARIA LTDA EPP REGISTRO FOTOGRÁFICO</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>DEIXAR O USAR O CINTO SEGURANCA</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
+          <t>AV JOHN BOYD DUNLOP X R PE EZEQUIEL RAMIN</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>CAMPINAS</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>6291</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>262910</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>PREF. DE SP CAMPINAS</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_262910A0759267155185.pdf</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\vencidas\notificacaoPenalidade_BSC4C89_262910A0759267155185.pdf</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>vencidas</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
-        </is>
+          <t>Vencidas</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>U102645067</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>262910U1026450676050</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>46254</v>
       </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" s="1" t="n">
+        <v>46254</v>
+      </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM AVANCAR O SINAL VERMELHO DO SEMAFORO - EXC HOUVER SINALIZ DESCONTO) PERM LIVRE CONV A DIREITA FISC ELETRONICA 20/08/2026</t>
-        </is>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>-48</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) CAMPINAS SP U102645067 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 15/07/2026</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 293,47</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>293.47</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>REGISTRO FOTOGRÁFICO JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO SN190722214BR IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>AVANCAR O SINAL VERMELHO DO SEMAFORO - EXC HOUVER SINALIZ</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>R. NADIR DIAS DE OLIVEIRA (BC) ESTACAO BANDEIRANTES F2/L105A</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>CAMPINAS</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>6291</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>262910</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>PREF. DE SP CAMPINAS</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_262910U1026450676050.pdf</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\vencidas\notificacaoPenalidade_BSC4C89_262910U1026450676050.pdf</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>vencidas</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
+          <t>Vencidas</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Z143749314</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>262910Z1437493145002</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>46195</v>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" s="1" t="n">
+        <v>46195</v>
+      </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM MULTA, POR NAO IDENTIFICACAO DO CONDUTOR INFRATOR, IMPOSTA DESCONTO) A PESSOA JURIDICA 22/06/2026</t>
-        </is>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>-107</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) CAMPINAS SP Z143749314 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 15/05/2026</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 390,46</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>390.46</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>REGISTRO FOTOGRÁFICO JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>FORD/CARGO 1415 NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>MULTA, POR NAO IMPOSTA</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
+          <t>RUA ANTONIO MANUEL, 50 - VILA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>CAMPINAS</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>6291</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>262910</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>PREF. DE SP CAMPINAS</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_262910Z1437493145002.pdf</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\vencidas\notificacaoPenalidade_BSC4C89_262910Z1437493145002.pdf</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>vencidas</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Vencidas</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Penalidade</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
+          <t>T490119869</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>264270T4901198697374</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>46087</v>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
+      <c r="I20" s="1" t="n">
+        <v>46087</v>
       </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>DATA DE VENCIMENTO DA PENALIDADE (DATA LIMITE PARA PAGAMENTO COM BLOQUEAR A VIA COM VEICULO DESCONTO) 06/03/2026</t>
-        </is>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>-215</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>UF IDENTIFICAÇÃO DO AUTO DE INFRAÇÃO (NÚMERO DO AIT) FRANCISCO MORATO SP T490119869 DATA DA NOTIFICAÇÃO DA PENALIDADE IDENTIFICAÇÃO DA INFRAÇÃO 20/01/2026</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>NOME DO MUNICÍPIO UF</t>
-        </is>
+          <t>R$ 293,47</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>293.47</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>JOANOPOLIS AGROPECUARIA LTDA EPP REGISTRO FOTOGRÁFICO</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NÚMERO DO EQUIPAMENTO OU INSTRUMENTO DE AFERIÇÃO FORD/CARGO 1415 Não disponível IDENTIFICAÇÃO DO CONDUTOR</t>
+          <t>BLOQUEAR A VIA COM VEICULO</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
+          <t>AV PAULO BROSSARD 1011</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>FRANCISCO MORATO</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>6427</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>264270</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>PREF. DE SP FRANCISCO</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>JOANOPOLIS AGROPECUARIA LTDA EPP</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>FORD/CARGO 1415</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
           <t>notificacaoPenalidade_BSC4C89_264270T4901198697374.pdf</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>a:\Multas\Placas\BSC4C89\vencidas\notificacaoPenalidade_BSC4C89_264270T4901198697374.pdf</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1652,17 +2724,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>placa</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>qtd_A_Vencer</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>qtd_Pagas</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>qtd_Vencidas</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>valor_total_A_Vencer</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>valor_total_Pagas</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>valor_total_Vencidas</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prazo_min_A_Vencer</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prazo_min_Pagas</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prazo_min_Vencidas</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>qtd_TOTAL</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>valor_total_TOTAL</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prazo_min_geral</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BSC4C89</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1628.22</v>
+      </c>
+      <c r="G2" t="n">
+        <v>586.9400000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2539.26</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-103</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-282</v>
+      </c>
+      <c r="L2" t="n">
+        <v>19</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4754.42</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-282</v>
       </c>
     </row>
   </sheetData>
